--- a/S_数据表/Activity_Template.xlsx
+++ b/S_数据表/Activity_Template.xlsx
@@ -1,26 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F874B8-3C3E-4A87-B447-051294E84C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D16418-1034-48FB-B3EF-3ADB58BE6057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -144,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="278">
   <si>
     <t>ID</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -1114,6 +1104,14 @@
   </si>
   <si>
     <t>冷却清空大礼包</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不朽大礼包</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000085,5;10000086,30;10000087,1;10000087,1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -13093,7 +13091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -13110,9 +13108,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -13125,11 +13120,8 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -13174,7 +13166,7 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13183,10 +13175,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="63" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="63" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="63" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13199,9 +13188,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="63" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3708">
@@ -17175,7 +17161,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A5:D125" tableType="xml" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4" connectionId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A5:D126" tableType="xml" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4" connectionId="1">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="ID" name="ID" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/DateArea/date/@ID" xmlDataType="string"/>
@@ -17191,9 +17177,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -17231,9 +17217,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -17266,26 +17252,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -17318,26 +17287,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -17511,7 +17463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P126"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="21.625" customWidth="1"/>
@@ -17521,7 +17473,7 @@
     <col min="6" max="7" width="40.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17543,10 +17495,8 @@
       <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -17568,10 +17518,8 @@
       <c r="G2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3">
         <v>8</v>
       </c>
@@ -17593,10 +17541,8 @@
       <c r="G3" s="3">
         <v>16</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -17618,10 +17564,8 @@
       <c r="G4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -17643,261 +17587,237 @@
       <c r="G5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6">
         <v>2001</v>
       </c>
       <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
+      <c r="G6" s="13"/>
     </row>
-    <row r="7" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="6">
         <v>2002</v>
       </c>
       <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
+      <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="6">
         <v>2003</v>
       </c>
       <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="G8" s="13"/>
     </row>
-    <row r="9" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="6">
         <v>2004</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="6">
         <v>2005</v>
       </c>
       <c r="B10" s="6">
         <v>2</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="G10" s="13"/>
     </row>
-    <row r="11" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="6">
         <v>2006</v>
       </c>
       <c r="B11" s="6">
         <v>2</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="G11" s="13"/>
     </row>
-    <row r="12" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="6">
         <v>2007</v>
       </c>
       <c r="B12" s="6">
         <v>2</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="13"/>
     </row>
-    <row r="13" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="6">
         <v>2008</v>
       </c>
       <c r="B13" s="6">
         <v>2</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="G13" s="13"/>
     </row>
-    <row r="14" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="6">
         <v>2009</v>
       </c>
       <c r="B14" s="6">
         <v>2</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
+      <c r="G14" s="13"/>
     </row>
-    <row r="15" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="6">
         <v>2010</v>
       </c>
       <c r="B15" s="6">
         <v>2</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
+      <c r="G15" s="13"/>
     </row>
-    <row r="16" spans="1:9" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="6">
         <v>3001</v>
       </c>
       <c r="B16" s="6">
         <v>3</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>1</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="6">
@@ -17906,21 +17826,19 @@
       <c r="B17" s="6">
         <v>3</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>1</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
+      <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="6">
@@ -17929,21 +17847,19 @@
       <c r="B18" s="6">
         <v>3</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>18</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="6">
@@ -17952,21 +17868,19 @@
       <c r="B19" s="6">
         <v>3</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>18</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="6">
@@ -17975,21 +17889,19 @@
       <c r="B20" s="6">
         <v>3</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>20</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="6">
@@ -17998,21 +17910,19 @@
       <c r="B21" s="6">
         <v>3</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>20</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="6">
@@ -18021,21 +17931,19 @@
       <c r="B22" s="6">
         <v>3</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>30</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="6">
@@ -18044,19 +17952,19 @@
       <c r="B23" s="6">
         <v>3</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>40</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="6">
@@ -18065,19 +17973,19 @@
       <c r="B24" s="6">
         <v>3</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>50</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="15"/>
+      <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="6">
@@ -18089,16 +17997,14 @@
       <c r="C25" s="6">
         <v>200000</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="6">
@@ -18110,16 +18016,14 @@
       <c r="C26" s="6">
         <v>90000</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="14" t="s">
+      <c r="E26" s="11"/>
+      <c r="F26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
+      <c r="G26" s="12"/>
     </row>
     <row r="27" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="6">
@@ -18131,16 +18035,14 @@
       <c r="C27" s="6">
         <v>100000</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="14" t="s">
+      <c r="E27" s="11"/>
+      <c r="F27" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
+      <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="6">
@@ -18152,16 +18054,14 @@
       <c r="C28" s="6">
         <v>200000</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="14" t="s">
+      <c r="E28" s="11"/>
+      <c r="F28" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="6">
@@ -18173,16 +18073,14 @@
       <c r="C29" s="6">
         <v>10000</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="14" t="s">
+      <c r="E29" s="11"/>
+      <c r="F29" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
+      <c r="G29" s="12"/>
     </row>
     <row r="30" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="6">
@@ -18194,17 +18092,15 @@
       <c r="C30" s="6">
         <v>200000</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="11"/>
+      <c r="F30" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="22"/>
+      <c r="G30" s="12"/>
+      <c r="J30" s="20"/>
     </row>
     <row r="31" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="6">
@@ -18216,17 +18112,15 @@
       <c r="C31" s="6">
         <v>200000</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="14" t="s">
+      <c r="E31" s="11"/>
+      <c r="F31" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="22"/>
+      <c r="G31" s="12"/>
+      <c r="J31" s="20"/>
     </row>
     <row r="32" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="6">
@@ -18238,29 +18132,29 @@
       <c r="C32" s="6">
         <v>1</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J32" s="22"/>
-      <c r="K32" s="7" t="s">
+      <c r="J32" s="20"/>
+      <c r="K32" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="L32" s="24">
+      <c r="L32" s="22">
         <v>1</v>
       </c>
-      <c r="M32" s="7">
+      <c r="M32" s="6">
         <v>1710</v>
       </c>
-      <c r="N32" s="24">
+      <c r="N32" s="22">
         <f>M32/100*2000</f>
         <v>34200</v>
       </c>
@@ -18275,29 +18169,29 @@
       <c r="C33" s="6">
         <v>18</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J33" s="22"/>
-      <c r="K33" s="7" t="s">
+      <c r="J33" s="20"/>
+      <c r="K33" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="L33" s="24">
+      <c r="L33" s="22">
         <v>1.4</v>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="6">
         <v>2085</v>
       </c>
-      <c r="N33" s="24">
+      <c r="N33" s="22">
         <f t="shared" ref="N33:N78" si="0">M33/100*2000</f>
         <v>41700</v>
       </c>
@@ -18312,29 +18206,29 @@
       <c r="C34" s="6">
         <v>30</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J34" s="22"/>
-      <c r="K34" s="7" t="s">
+      <c r="J34" s="20"/>
+      <c r="K34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="22">
         <v>1.8</v>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="6">
         <v>2460</v>
       </c>
-      <c r="N34" s="24">
+      <c r="N34" s="22">
         <f t="shared" si="0"/>
         <v>49200</v>
       </c>
@@ -18349,29 +18243,29 @@
       <c r="C35" s="6">
         <v>40</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J35" s="22"/>
-      <c r="K35" s="7" t="s">
+      <c r="J35" s="20"/>
+      <c r="K35" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="L35" s="24">
+      <c r="L35" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="6">
         <v>2835</v>
       </c>
-      <c r="N35" s="24">
+      <c r="N35" s="22">
         <f t="shared" si="0"/>
         <v>56700</v>
       </c>
@@ -18386,29 +18280,29 @@
       <c r="C36" s="6">
         <v>50</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J36" s="22"/>
-      <c r="K36" s="7" t="s">
+      <c r="J36" s="20"/>
+      <c r="K36" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L36" s="24">
+      <c r="L36" s="22">
         <v>2.6</v>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="6">
         <v>3135</v>
       </c>
-      <c r="N36" s="24">
+      <c r="N36" s="22">
         <f t="shared" si="0"/>
         <v>62700</v>
       </c>
@@ -18423,29 +18317,29 @@
       <c r="C37" s="6">
         <v>1</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J37" s="22"/>
-      <c r="K37" s="7" t="s">
+      <c r="J37" s="20"/>
+      <c r="K37" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L37" s="24">
+      <c r="L37" s="22">
         <v>1</v>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="6">
         <v>620</v>
       </c>
-      <c r="N37" s="24">
+      <c r="N37" s="22">
         <f t="shared" si="0"/>
         <v>12400</v>
       </c>
@@ -18460,34 +18354,34 @@
       <c r="C38" s="6">
         <v>18</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J38" s="21"/>
-      <c r="K38" s="7" t="s">
+      <c r="J38" s="19"/>
+      <c r="K38" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="L38" s="24">
+      <c r="L38" s="22">
         <v>1.4</v>
       </c>
-      <c r="M38" s="7">
+      <c r="M38" s="6">
         <v>770</v>
       </c>
-      <c r="N38" s="24">
+      <c r="N38" s="22">
         <f t="shared" si="0"/>
         <v>15400</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="6">
         <v>20203</v>
       </c>
@@ -18497,34 +18391,34 @@
       <c r="C39" s="6">
         <v>30</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E39" s="23" t="s">
+      <c r="E39" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J39" s="22"/>
-      <c r="K39" s="7" t="s">
+      <c r="J39" s="20"/>
+      <c r="K39" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="22">
         <v>1.8</v>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="6">
         <v>920</v>
       </c>
-      <c r="N39" s="24">
+      <c r="N39" s="22">
         <f t="shared" si="0"/>
         <v>18400</v>
       </c>
     </row>
-    <row r="40" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="6">
         <v>20204</v>
       </c>
@@ -18534,34 +18428,34 @@
       <c r="C40" s="6">
         <v>40</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E40" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J40" s="22"/>
-      <c r="K40" s="7" t="s">
+      <c r="J40" s="20"/>
+      <c r="K40" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="L40" s="24">
+      <c r="L40" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="6">
         <v>1070</v>
       </c>
-      <c r="N40" s="24">
+      <c r="N40" s="22">
         <f t="shared" si="0"/>
         <v>21400</v>
       </c>
     </row>
-    <row r="41" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="6">
         <v>20205</v>
       </c>
@@ -18571,35 +18465,35 @@
       <c r="C41" s="6">
         <v>50</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="E41" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="J41" s="22"/>
-      <c r="K41" s="7" t="s">
+      <c r="J41" s="20"/>
+      <c r="K41" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L41" s="24">
+      <c r="L41" s="22">
         <v>2.6</v>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="6">
         <v>1220</v>
       </c>
-      <c r="N41" s="24">
+      <c r="N41" s="22">
         <f t="shared" si="0"/>
         <v>24400</v>
       </c>
     </row>
-    <row r="42" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="11">
+    <row r="42" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="10">
         <v>20301</v>
       </c>
       <c r="B42" s="6">
@@ -18608,35 +18502,35 @@
       <c r="C42" s="6">
         <v>1</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J42" s="22"/>
-      <c r="K42" s="7" t="s">
+      <c r="J42" s="20"/>
+      <c r="K42" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="L42" s="24">
+      <c r="L42" s="22">
         <v>1</v>
       </c>
-      <c r="M42" s="7">
+      <c r="M42" s="6">
         <v>1520</v>
       </c>
-      <c r="N42" s="24">
+      <c r="N42" s="22">
         <f t="shared" si="0"/>
         <v>30400</v>
       </c>
     </row>
-    <row r="43" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="11">
+    <row r="43" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="10">
         <v>20302</v>
       </c>
       <c r="B43" s="6">
@@ -18645,35 +18539,35 @@
       <c r="C43" s="6">
         <v>18</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="E43" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J43" s="22"/>
-      <c r="K43" s="7" t="s">
+      <c r="J43" s="20"/>
+      <c r="K43" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="L43" s="24">
+      <c r="L43" s="22">
         <v>1.4</v>
       </c>
-      <c r="M43" s="7">
+      <c r="M43" s="6">
         <v>1820</v>
       </c>
-      <c r="N43" s="24">
+      <c r="N43" s="22">
         <f t="shared" si="0"/>
         <v>36400</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="11">
+    <row r="44" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="10">
         <v>20303</v>
       </c>
       <c r="B44" s="6">
@@ -18682,35 +18576,35 @@
       <c r="C44" s="6">
         <v>30</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J44" s="22"/>
-      <c r="K44" s="7" t="s">
+      <c r="J44" s="20"/>
+      <c r="K44" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L44" s="24">
+      <c r="L44" s="22">
         <v>1.8</v>
       </c>
-      <c r="M44" s="7">
+      <c r="M44" s="6">
         <v>2120</v>
       </c>
-      <c r="N44" s="24">
+      <c r="N44" s="22">
         <f t="shared" si="0"/>
         <v>42400</v>
       </c>
     </row>
-    <row r="45" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="11">
+    <row r="45" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="10">
         <v>20304</v>
       </c>
       <c r="B45" s="6">
@@ -18719,35 +18613,35 @@
       <c r="C45" s="6">
         <v>40</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E45" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J45" s="22"/>
-      <c r="K45" s="7" t="s">
+      <c r="J45" s="20"/>
+      <c r="K45" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="L45" s="24">
+      <c r="L45" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M45" s="7">
+      <c r="M45" s="6">
         <v>2420</v>
       </c>
-      <c r="N45" s="24">
+      <c r="N45" s="22">
         <f t="shared" si="0"/>
         <v>48400</v>
       </c>
     </row>
-    <row r="46" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="11">
+    <row r="46" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="10">
         <v>20305</v>
       </c>
       <c r="B46" s="6">
@@ -18756,35 +18650,35 @@
       <c r="C46" s="6">
         <v>50</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="23" t="s">
+      <c r="E46" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J46" s="22"/>
-      <c r="K46" s="7" t="s">
+      <c r="J46" s="20"/>
+      <c r="K46" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L46" s="22">
         <v>2.6</v>
       </c>
-      <c r="M46" s="7">
+      <c r="M46" s="6">
         <v>2720</v>
       </c>
-      <c r="N46" s="24">
+      <c r="N46" s="22">
         <f t="shared" si="0"/>
         <v>54400</v>
       </c>
     </row>
-    <row r="47" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="11">
+    <row r="47" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="10">
         <v>20401</v>
       </c>
       <c r="B47" s="6">
@@ -18793,35 +18687,35 @@
       <c r="C47" s="6">
         <v>1</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J47" s="22"/>
-      <c r="K47" s="7" t="s">
+      <c r="J47" s="20"/>
+      <c r="K47" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L47" s="24">
+      <c r="L47" s="22">
         <v>1</v>
       </c>
-      <c r="M47" s="7">
+      <c r="M47" s="6">
         <v>720</v>
       </c>
-      <c r="N47" s="24">
+      <c r="N47" s="22">
         <f t="shared" si="0"/>
         <v>14400</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="11">
+      <c r="A48" s="10">
         <v>20402</v>
       </c>
       <c r="B48" s="6">
@@ -18830,35 +18724,35 @@
       <c r="C48" s="6">
         <v>18</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J48" s="21"/>
-      <c r="K48" s="7" t="s">
+      <c r="J48" s="19"/>
+      <c r="K48" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="L48" s="24">
+      <c r="L48" s="22">
         <v>1.4</v>
       </c>
-      <c r="M48" s="7">
+      <c r="M48" s="6">
         <v>920</v>
       </c>
-      <c r="N48" s="24">
+      <c r="N48" s="22">
         <f t="shared" si="0"/>
         <v>18400</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="11">
+      <c r="A49" s="10">
         <v>20403</v>
       </c>
       <c r="B49" s="6">
@@ -18867,35 +18761,35 @@
       <c r="C49" s="6">
         <v>30</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J49" s="21"/>
-      <c r="K49" s="7" t="s">
+      <c r="J49" s="19"/>
+      <c r="K49" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="L49" s="24">
+      <c r="L49" s="22">
         <v>1.8</v>
       </c>
-      <c r="M49" s="7">
+      <c r="M49" s="6">
         <v>1120</v>
       </c>
-      <c r="N49" s="24">
+      <c r="N49" s="22">
         <f t="shared" si="0"/>
         <v>22400</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="11">
+      <c r="A50" s="10">
         <v>20404</v>
       </c>
       <c r="B50" s="6">
@@ -18904,35 +18798,35 @@
       <c r="C50" s="6">
         <v>40</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J50" s="21"/>
-      <c r="K50" s="7" t="s">
+      <c r="J50" s="19"/>
+      <c r="K50" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="L50" s="24">
+      <c r="L50" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M50" s="7">
+      <c r="M50" s="6">
         <v>1320</v>
       </c>
-      <c r="N50" s="24">
+      <c r="N50" s="22">
         <f t="shared" si="0"/>
         <v>26400</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="11">
+      <c r="A51" s="10">
         <v>20405</v>
       </c>
       <c r="B51" s="6">
@@ -18941,35 +18835,35 @@
       <c r="C51" s="6">
         <v>50</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J51" s="21"/>
-      <c r="K51" s="7" t="s">
+      <c r="J51" s="19"/>
+      <c r="K51" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="L51" s="24">
+      <c r="L51" s="22">
         <v>2.6</v>
       </c>
-      <c r="M51" s="7">
+      <c r="M51" s="6">
         <v>1520</v>
       </c>
-      <c r="N51" s="24">
+      <c r="N51" s="22">
         <f t="shared" si="0"/>
         <v>30400</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="11">
+      <c r="A52" s="10">
         <v>20501</v>
       </c>
       <c r="B52" s="6">
@@ -18978,35 +18872,35 @@
       <c r="C52" s="6">
         <v>1</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="J52" s="21"/>
-      <c r="K52" s="7" t="s">
+      <c r="J52" s="19"/>
+      <c r="K52" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L52" s="24">
+      <c r="L52" s="22">
         <v>1</v>
       </c>
-      <c r="M52" s="7">
+      <c r="M52" s="6">
         <v>1140</v>
       </c>
-      <c r="N52" s="24">
+      <c r="N52" s="22">
         <f t="shared" si="0"/>
         <v>22800</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="11">
+      <c r="A53" s="10">
         <v>20502</v>
       </c>
       <c r="B53" s="6">
@@ -19015,35 +18909,35 @@
       <c r="C53" s="6">
         <v>18</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="J53" s="21"/>
-      <c r="K53" s="7" t="s">
+      <c r="J53" s="19"/>
+      <c r="K53" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="24">
+      <c r="L53" s="22">
         <v>1.4</v>
       </c>
-      <c r="M53" s="7">
+      <c r="M53" s="6">
         <v>1800</v>
       </c>
-      <c r="N53" s="24">
+      <c r="N53" s="22">
         <f t="shared" si="0"/>
         <v>36000</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="11">
+      <c r="A54" s="10">
         <v>20503</v>
       </c>
       <c r="B54" s="6">
@@ -19052,35 +18946,35 @@
       <c r="C54" s="6">
         <v>30</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="J54" s="21"/>
-      <c r="K54" s="7" t="s">
+      <c r="J54" s="19"/>
+      <c r="K54" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="L54" s="24">
+      <c r="L54" s="22">
         <v>1.8</v>
       </c>
-      <c r="M54" s="7">
+      <c r="M54" s="6">
         <v>2540</v>
       </c>
-      <c r="N54" s="24">
+      <c r="N54" s="22">
         <f t="shared" si="0"/>
         <v>50800</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="11">
+      <c r="A55" s="10">
         <v>20504</v>
       </c>
       <c r="B55" s="6">
@@ -19089,35 +18983,35 @@
       <c r="C55" s="6">
         <v>40</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="J55" s="21"/>
-      <c r="K55" s="7" t="s">
+      <c r="J55" s="19"/>
+      <c r="K55" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="L55" s="24">
+      <c r="L55" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M55" s="7">
+      <c r="M55" s="6">
         <v>3360</v>
       </c>
-      <c r="N55" s="24">
+      <c r="N55" s="22">
         <f t="shared" si="0"/>
         <v>67200</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="11">
+      <c r="A56" s="10">
         <v>20505</v>
       </c>
       <c r="B56" s="6">
@@ -19126,35 +19020,35 @@
       <c r="C56" s="6">
         <v>50</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G56" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="J56" s="21"/>
-      <c r="K56" s="7" t="s">
+      <c r="J56" s="19"/>
+      <c r="K56" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="L56" s="24">
+      <c r="L56" s="22">
         <v>2.6</v>
       </c>
-      <c r="M56" s="7">
+      <c r="M56" s="6">
         <v>4260</v>
       </c>
-      <c r="N56" s="24">
+      <c r="N56" s="22">
         <f t="shared" si="0"/>
         <v>85200</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="11">
+      <c r="A57" s="10">
         <v>20601</v>
       </c>
       <c r="B57" s="6">
@@ -19163,35 +19057,35 @@
       <c r="C57" s="6">
         <v>1</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G57" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J57" s="21"/>
-      <c r="K57" s="7" t="s">
+      <c r="J57" s="19"/>
+      <c r="K57" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="L57" s="24">
+      <c r="L57" s="22">
         <v>1</v>
       </c>
-      <c r="M57" s="7">
+      <c r="M57" s="6">
         <v>1560</v>
       </c>
-      <c r="N57" s="24">
+      <c r="N57" s="22">
         <f t="shared" si="0"/>
         <v>31200</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="11">
+      <c r="A58" s="10">
         <v>20602</v>
       </c>
       <c r="B58" s="6">
@@ -19200,35 +19094,35 @@
       <c r="C58" s="6">
         <v>18</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G58" s="7" t="s">
+      <c r="G58" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J58" s="21"/>
-      <c r="K58" s="7" t="s">
+      <c r="J58" s="19"/>
+      <c r="K58" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="L58" s="24">
+      <c r="L58" s="22">
         <v>1.4</v>
       </c>
-      <c r="M58" s="7">
+      <c r="M58" s="6">
         <v>1720</v>
       </c>
-      <c r="N58" s="24">
+      <c r="N58" s="22">
         <f t="shared" si="0"/>
         <v>34400</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="11">
+      <c r="A59" s="10">
         <v>20603</v>
       </c>
       <c r="B59" s="6">
@@ -19237,35 +19131,35 @@
       <c r="C59" s="6">
         <v>30</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G59" s="7" t="s">
+      <c r="G59" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J59" s="21"/>
-      <c r="K59" s="7" t="s">
+      <c r="J59" s="19"/>
+      <c r="K59" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="L59" s="24">
+      <c r="L59" s="22">
         <v>1.8</v>
       </c>
-      <c r="M59" s="7">
+      <c r="M59" s="6">
         <v>1880</v>
       </c>
-      <c r="N59" s="24">
+      <c r="N59" s="22">
         <f t="shared" si="0"/>
         <v>37600</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="11">
+      <c r="A60" s="10">
         <v>20604</v>
       </c>
       <c r="B60" s="6">
@@ -19274,35 +19168,35 @@
       <c r="C60" s="6">
         <v>40</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G60" s="7" t="s">
+      <c r="G60" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J60" s="21"/>
-      <c r="K60" s="7" t="s">
+      <c r="J60" s="19"/>
+      <c r="K60" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="L60" s="24">
+      <c r="L60" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M60" s="7">
+      <c r="M60" s="6">
         <v>2040</v>
       </c>
-      <c r="N60" s="24">
+      <c r="N60" s="22">
         <f t="shared" si="0"/>
         <v>40800</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="11">
+      <c r="A61" s="10">
         <v>20605</v>
       </c>
       <c r="B61" s="6">
@@ -19311,71 +19205,71 @@
       <c r="C61" s="6">
         <v>50</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G61" s="7" t="s">
+      <c r="G61" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J61" s="21"/>
-      <c r="K61" s="7" t="s">
+      <c r="J61" s="19"/>
+      <c r="K61" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="L61" s="24">
+      <c r="L61" s="22">
         <v>2.6</v>
       </c>
-      <c r="M61" s="7">
+      <c r="M61" s="6">
         <v>2200</v>
       </c>
-      <c r="N61" s="24">
+      <c r="N61" s="22">
         <f t="shared" si="0"/>
         <v>44000</v>
       </c>
     </row>
-    <row r="62" spans="1:14" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="31">
+    <row r="62" spans="1:14" s="31" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="29">
         <v>20606</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="30">
         <v>2</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="30">
         <v>55</v>
       </c>
-      <c r="D62" s="30" t="s">
+      <c r="D62" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="E62" s="37" t="s">
+      <c r="E62" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="F62" s="33" t="s">
+      <c r="F62" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="G62" s="33" t="s">
+      <c r="G62" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="J62" s="35"/>
-      <c r="K62" s="33" t="s">
+      <c r="J62" s="32"/>
+      <c r="K62" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="L62" s="36">
+      <c r="L62" s="33">
         <v>2.6</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="30">
         <v>2200</v>
       </c>
-      <c r="N62" s="36">
+      <c r="N62" s="33">
         <v>44000</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="11">
+      <c r="A63" s="10">
         <v>20701</v>
       </c>
       <c r="B63" s="6">
@@ -19384,35 +19278,35 @@
       <c r="C63" s="6">
         <v>1</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J63" s="21"/>
-      <c r="K63" s="7" t="s">
+      <c r="J63" s="19"/>
+      <c r="K63" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="L63" s="24">
+      <c r="L63" s="22">
         <v>1</v>
       </c>
-      <c r="M63" s="7">
+      <c r="M63" s="6">
         <v>2200</v>
       </c>
-      <c r="N63" s="24">
+      <c r="N63" s="22">
         <f t="shared" si="0"/>
         <v>44000</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="11">
+      <c r="A64" s="10">
         <v>20702</v>
       </c>
       <c r="B64" s="6">
@@ -19421,35 +19315,35 @@
       <c r="C64" s="6">
         <v>18</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J64" s="21"/>
-      <c r="K64" s="7" t="s">
+      <c r="J64" s="19"/>
+      <c r="K64" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="L64" s="24">
+      <c r="L64" s="22">
         <v>1.4</v>
       </c>
-      <c r="M64" s="7">
+      <c r="M64" s="6">
         <v>2440</v>
       </c>
-      <c r="N64" s="24">
+      <c r="N64" s="22">
         <f t="shared" si="0"/>
         <v>48800</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="11">
+      <c r="A65" s="10">
         <v>20703</v>
       </c>
       <c r="B65" s="6">
@@ -19458,35 +19352,35 @@
       <c r="C65" s="6">
         <v>30</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G65" s="7" t="s">
+      <c r="G65" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J65" s="21"/>
-      <c r="K65" s="7" t="s">
+      <c r="J65" s="19"/>
+      <c r="K65" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="L65" s="24">
+      <c r="L65" s="22">
         <v>1.8</v>
       </c>
-      <c r="M65" s="7">
+      <c r="M65" s="6">
         <v>2680</v>
       </c>
-      <c r="N65" s="24">
+      <c r="N65" s="22">
         <f t="shared" si="0"/>
         <v>53600</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="11">
+      <c r="A66" s="10">
         <v>20704</v>
       </c>
       <c r="B66" s="6">
@@ -19495,35 +19389,35 @@
       <c r="C66" s="6">
         <v>40</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G66" s="7" t="s">
+      <c r="G66" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J66" s="21"/>
-      <c r="K66" s="7" t="s">
+      <c r="J66" s="19"/>
+      <c r="K66" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="L66" s="24">
+      <c r="L66" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M66" s="7">
+      <c r="M66" s="6">
         <v>3000</v>
       </c>
-      <c r="N66" s="24">
+      <c r="N66" s="22">
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="11">
+      <c r="A67" s="10">
         <v>20705</v>
       </c>
       <c r="B67" s="6">
@@ -19532,71 +19426,71 @@
       <c r="C67" s="6">
         <v>50</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J67" s="21"/>
-      <c r="K67" s="7" t="s">
+      <c r="J67" s="19"/>
+      <c r="K67" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="L67" s="24">
+      <c r="L67" s="22">
         <v>2.6</v>
       </c>
-      <c r="M67" s="7">
+      <c r="M67" s="6">
         <v>3320</v>
       </c>
-      <c r="N67" s="24">
+      <c r="N67" s="22">
         <f t="shared" si="0"/>
         <v>66400</v>
       </c>
     </row>
-    <row r="68" spans="1:14" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="31">
+    <row r="68" spans="1:14" s="31" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="29">
         <v>20706</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="30">
         <v>2</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="30">
         <v>55</v>
       </c>
-      <c r="D68" s="30" t="s">
+      <c r="D68" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="E68" s="37" t="s">
+      <c r="E68" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="G68" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="J68" s="35"/>
-      <c r="K68" s="33" t="s">
+      <c r="J68" s="32"/>
+      <c r="K68" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="L68" s="36">
+      <c r="L68" s="33">
         <v>2.6</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="30">
         <v>2200</v>
       </c>
-      <c r="N68" s="36">
+      <c r="N68" s="33">
         <v>44000</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="11">
+      <c r="A69" s="10">
         <v>20801</v>
       </c>
       <c r="B69" s="6">
@@ -19605,35 +19499,35 @@
       <c r="C69" s="6">
         <v>1</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="G69" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J69" s="21"/>
-      <c r="K69" s="7" t="s">
+      <c r="J69" s="19"/>
+      <c r="K69" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="L69" s="24">
+      <c r="L69" s="22">
         <v>1</v>
       </c>
-      <c r="M69" s="7">
+      <c r="M69" s="6">
         <v>2040</v>
       </c>
-      <c r="N69" s="24">
+      <c r="N69" s="22">
         <f t="shared" si="0"/>
         <v>40800</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="11">
+      <c r="A70" s="10">
         <v>20802</v>
       </c>
       <c r="B70" s="6">
@@ -19642,35 +19536,35 @@
       <c r="C70" s="6">
         <v>18</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G70" s="7" t="s">
+      <c r="G70" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J70" s="21"/>
-      <c r="K70" s="7" t="s">
+      <c r="J70" s="19"/>
+      <c r="K70" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="L70" s="24">
+      <c r="L70" s="22">
         <v>1.4</v>
       </c>
-      <c r="M70" s="7">
+      <c r="M70" s="6">
         <v>2240</v>
       </c>
-      <c r="N70" s="24">
+      <c r="N70" s="22">
         <f t="shared" si="0"/>
         <v>44800</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="11">
+      <c r="A71" s="10">
         <v>20803</v>
       </c>
       <c r="B71" s="6">
@@ -19679,35 +19573,35 @@
       <c r="C71" s="6">
         <v>30</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E71" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="F71" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G71" s="7" t="s">
+      <c r="G71" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J71" s="21"/>
-      <c r="K71" s="7" t="s">
+      <c r="J71" s="19"/>
+      <c r="K71" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="L71" s="24">
+      <c r="L71" s="22">
         <v>1.8</v>
       </c>
-      <c r="M71" s="7">
+      <c r="M71" s="6">
         <v>2440</v>
       </c>
-      <c r="N71" s="24">
+      <c r="N71" s="22">
         <f t="shared" si="0"/>
         <v>48800</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="11">
+      <c r="A72" s="10">
         <v>20804</v>
       </c>
       <c r="B72" s="6">
@@ -19716,35 +19610,35 @@
       <c r="C72" s="6">
         <v>40</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G72" s="7" t="s">
+      <c r="G72" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J72" s="21"/>
-      <c r="K72" s="7" t="s">
+      <c r="J72" s="19"/>
+      <c r="K72" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="L72" s="24">
+      <c r="L72" s="22">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M72" s="7">
+      <c r="M72" s="6">
         <v>2640</v>
       </c>
-      <c r="N72" s="24">
+      <c r="N72" s="22">
         <f t="shared" si="0"/>
         <v>52800</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="11">
+      <c r="A73" s="10">
         <v>20805</v>
       </c>
       <c r="B73" s="6">
@@ -19753,35 +19647,35 @@
       <c r="C73" s="6">
         <v>50</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="F73" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G73" s="7" t="s">
+      <c r="G73" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J73" s="21"/>
-      <c r="K73" s="7" t="s">
+      <c r="J73" s="19"/>
+      <c r="K73" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="L73" s="24">
+      <c r="L73" s="22">
         <v>2.6</v>
       </c>
-      <c r="M73" s="7">
+      <c r="M73" s="6">
         <v>3240</v>
       </c>
-      <c r="N73" s="24">
+      <c r="N73" s="22">
         <f t="shared" si="0"/>
         <v>64800</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="11">
+      <c r="A74" s="10">
         <v>20806</v>
       </c>
       <c r="B74" s="6">
@@ -19790,35 +19684,35 @@
       <c r="C74" s="6">
         <v>60</v>
       </c>
-      <c r="D74" s="27" t="s">
+      <c r="D74" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="E74" s="37" t="s">
+      <c r="E74" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="F74" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="G74" s="7" t="s">
+      <c r="G74" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J74" s="21"/>
-      <c r="K74" s="7" t="s">
+      <c r="J74" s="19"/>
+      <c r="K74" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="L74" s="24">
+      <c r="L74" s="22">
         <v>2.6</v>
       </c>
-      <c r="M74" s="7">
+      <c r="M74" s="6">
         <v>3240</v>
       </c>
-      <c r="N74" s="24">
+      <c r="N74" s="22">
         <f t="shared" ref="N74" si="1">M74/100*2000</f>
         <v>64800</v>
       </c>
     </row>
-    <row r="75" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="11">
+    <row r="75" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="10">
         <v>21001</v>
       </c>
       <c r="B75" s="6">
@@ -19827,32 +19721,32 @@
       <c r="C75" s="6">
         <v>1</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E75" s="23" t="s">
+      <c r="E75" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F75" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G75" s="7" t="s">
+      <c r="G75" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="J75" s="22"/>
-      <c r="K75" s="7" t="s">
+      <c r="J75" s="20"/>
+      <c r="K75" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="M75" s="7">
+      <c r="M75" s="6">
         <v>2040</v>
       </c>
-      <c r="N75" s="24">
+      <c r="N75" s="22">
         <f t="shared" si="0"/>
         <v>40800</v>
       </c>
     </row>
-    <row r="76" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="11">
+    <row r="76" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="10">
         <v>21002</v>
       </c>
       <c r="B76" s="6">
@@ -19861,32 +19755,32 @@
       <c r="C76" s="6">
         <v>1</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E76" s="23" t="s">
+      <c r="E76" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F76" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="G76" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="J76" s="22"/>
-      <c r="K76" s="7" t="s">
+      <c r="J76" s="20"/>
+      <c r="K76" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="M76" s="7">
+      <c r="M76" s="6">
         <v>3240</v>
       </c>
-      <c r="N76" s="24">
+      <c r="N76" s="22">
         <f t="shared" si="0"/>
         <v>64800</v>
       </c>
     </row>
-    <row r="77" spans="1:14" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="11">
+    <row r="77" spans="1:14" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="10">
         <v>21003</v>
       </c>
       <c r="B77" s="6">
@@ -19895,32 +19789,32 @@
       <c r="C77" s="6">
         <v>1</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E77" s="23" t="s">
+      <c r="E77" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J77" s="22"/>
-      <c r="K77" s="7" t="s">
+      <c r="J77" s="20"/>
+      <c r="K77" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="M77" s="7">
+      <c r="M77" s="6">
         <v>4120</v>
       </c>
-      <c r="N77" s="24">
+      <c r="N77" s="22">
         <f t="shared" si="0"/>
         <v>82400</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="11">
+      <c r="A78" s="10">
         <v>21004</v>
       </c>
       <c r="B78" s="6">
@@ -19929,32 +19823,32 @@
       <c r="C78" s="6">
         <v>1</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E78" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="G78" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="J78" s="21"/>
-      <c r="K78" s="7" t="s">
+      <c r="J78" s="19"/>
+      <c r="K78" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="M78" s="7">
+      <c r="M78" s="6">
         <v>4840</v>
       </c>
-      <c r="N78" s="24">
+      <c r="N78" s="22">
         <f t="shared" si="0"/>
         <v>96800</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="11">
+      <c r="A79" s="10">
         <v>21101</v>
       </c>
       <c r="B79" s="6">
@@ -19963,26 +19857,26 @@
       <c r="C79" s="6">
         <v>1</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F79" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G79" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="J79" s="21"/>
-      <c r="K79" s="7" t="s">
+      <c r="J79" s="19"/>
+      <c r="K79" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="M79" s="7">
+      <c r="M79" s="6">
         <v>4840</v>
       </c>
-      <c r="N79" s="24">
+      <c r="N79" s="22">
         <f t="shared" ref="N79" si="2">M79/100*2000</f>
         <v>96800</v>
       </c>
@@ -19994,23 +19888,23 @@
       <c r="B80" s="6">
         <v>2</v>
       </c>
-      <c r="C80" s="38">
+      <c r="C80" s="7">
         <v>55</v>
       </c>
-      <c r="D80" s="30" t="s">
+      <c r="D80" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="E80" s="17" t="s">
+      <c r="E80" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="F80" s="7" t="s">
+      <c r="F80" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G80" s="7"/>
-      <c r="J80" s="21"/>
-      <c r="K80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="24"/>
+      <c r="G80" s="6"/>
+      <c r="J80" s="19"/>
+      <c r="K80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="22"/>
     </row>
     <row r="81" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="6">
@@ -20019,23 +19913,23 @@
       <c r="B81" s="6">
         <v>2</v>
       </c>
-      <c r="C81" s="38">
+      <c r="C81" s="7">
         <v>55</v>
       </c>
-      <c r="D81" s="30" t="s">
+      <c r="D81" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="F81" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G81" s="7"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="24"/>
+      <c r="G81" s="6"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="22"/>
     </row>
     <row r="82" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="6">
@@ -20044,1470 +19938,1495 @@
       <c r="B82" s="6">
         <v>2</v>
       </c>
-      <c r="C82" s="38">
+      <c r="C82" s="7">
         <v>55</v>
       </c>
-      <c r="D82" s="30" t="s">
+      <c r="D82" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E82" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="F82" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="G82" s="7"/>
-      <c r="J82" s="21"/>
-      <c r="K82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="24"/>
+      <c r="G82" s="6"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="22"/>
     </row>
     <row r="83" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="6">
-        <v>30001</v>
+        <v>21501</v>
       </c>
       <c r="B83" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" s="7">
-        <v>1</v>
-      </c>
-      <c r="D83" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E83" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="F83" s="7" t="str">
-        <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>1级等级礼包</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="J83" s="21"/>
-      <c r="K83" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L83" s="24">
-        <v>1</v>
-      </c>
-      <c r="M83" s="7">
-        <v>1450</v>
-      </c>
-      <c r="N83" s="24">
-        <f>M83/100*2000*L83</f>
-        <v>29000</v>
-      </c>
-      <c r="P83" s="24" t="str">
-        <f>"1,"&amp;N83</f>
-        <v>1,29000</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="G83" s="6"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="22"/>
     </row>
     <row r="84" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="6">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="B84" s="6">
         <v>3</v>
       </c>
-      <c r="C84" s="7">
-        <v>5</v>
-      </c>
-      <c r="D84" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="F84" s="7" t="str">
+      <c r="C84" s="6">
+        <v>1</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F84" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>5级等级礼包</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I84" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="K84" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L84" s="24">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="M84" s="7">
-        <v>2025</v>
-      </c>
-      <c r="N84" s="24">
-        <f t="shared" ref="N84:N86" si="3">M84/100*2000*L84</f>
-        <v>44550</v>
-      </c>
-      <c r="P84" s="24" t="str">
-        <f t="shared" ref="P84:P105" si="4">"1,"&amp;N84</f>
-        <v>1,44550</v>
+        <v>1级等级礼包</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J84" s="19"/>
+      <c r="K84" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L84" s="22">
+        <v>1</v>
+      </c>
+      <c r="M84" s="6">
+        <v>1450</v>
+      </c>
+      <c r="N84" s="22">
+        <f>M84/100*2000*L84</f>
+        <v>29000</v>
+      </c>
+      <c r="P84" s="22" t="str">
+        <f>"1,"&amp;N84</f>
+        <v>1,29000</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="6">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="B85" s="6">
         <v>3</v>
       </c>
-      <c r="C85" s="7">
-        <v>10</v>
-      </c>
-      <c r="D85" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F85" s="7" t="str">
+      <c r="C85" s="6">
+        <v>5</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F85" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>10级等级礼包</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I85" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="J85" s="21"/>
-      <c r="K85" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L85" s="24">
-        <v>1.2</v>
-      </c>
-      <c r="M85" s="7">
-        <v>2700</v>
-      </c>
-      <c r="N85" s="24">
-        <f t="shared" si="3"/>
-        <v>64800</v>
-      </c>
-      <c r="P85" s="24" t="str">
-        <f t="shared" si="4"/>
-        <v>1,64800</v>
+        <v>5级等级礼包</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I85" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L85" s="22">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M85" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N85" s="22">
+        <f t="shared" ref="N85:N87" si="3">M85/100*2000*L85</f>
+        <v>44550</v>
+      </c>
+      <c r="P85" s="22" t="str">
+        <f t="shared" ref="P85:P106" si="4">"1,"&amp;N85</f>
+        <v>1,44550</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="6">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="B86" s="6">
         <v>3</v>
       </c>
-      <c r="C86" s="9">
-        <v>12</v>
-      </c>
-      <c r="D86" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="E86" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="F86" s="7" t="str">
+      <c r="C86" s="6">
+        <v>10</v>
+      </c>
+      <c r="D86" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F86" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>12级等级礼包</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="J86" s="21"/>
-      <c r="K86" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L86" s="24">
-        <v>1.3</v>
-      </c>
-      <c r="M86" s="7">
-        <v>1450</v>
-      </c>
-      <c r="N86" s="24">
+        <v>10级等级礼包</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I86" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J86" s="19"/>
+      <c r="K86" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L86" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="M86" s="6">
+        <v>2700</v>
+      </c>
+      <c r="N86" s="22">
         <f t="shared" si="3"/>
-        <v>37700</v>
-      </c>
-      <c r="P86" s="24" t="str">
+        <v>64800</v>
+      </c>
+      <c r="P86" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,37700</v>
+        <v>1,64800</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="6">
-        <v>30005</v>
-      </c>
-      <c r="B87" s="28">
+        <v>30004</v>
+      </c>
+      <c r="B87" s="6">
         <v>3</v>
       </c>
-      <c r="C87" s="29">
-        <v>18</v>
-      </c>
-      <c r="D87" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="E87" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J87" s="21"/>
-      <c r="K87" s="7"/>
-      <c r="L87" s="24"/>
-      <c r="M87" s="7"/>
-      <c r="N87" s="24"/>
-      <c r="P87" s="24"/>
+      <c r="C87" s="8">
+        <v>12</v>
+      </c>
+      <c r="D87" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F87" s="6" t="str">
+        <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
+        <v>12级等级礼包</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="J87" s="19"/>
+      <c r="K87" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L87" s="22">
+        <v>1.3</v>
+      </c>
+      <c r="M87" s="6">
+        <v>1450</v>
+      </c>
+      <c r="N87" s="22">
+        <f t="shared" si="3"/>
+        <v>37700</v>
+      </c>
+      <c r="P87" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>1,37700</v>
+      </c>
     </row>
     <row r="88" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="6">
-        <v>30006</v>
-      </c>
-      <c r="B88" s="6">
+        <v>30005</v>
+      </c>
+      <c r="B88" s="26">
         <v>3</v>
       </c>
-      <c r="C88" s="9">
-        <v>20</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F88" s="7" t="str">
-        <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>20级等级礼包</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="H88" s="17"/>
-      <c r="I88" s="21"/>
-      <c r="J88" s="21"/>
-      <c r="K88" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L88" s="24">
-        <v>1.4</v>
-      </c>
-      <c r="M88" s="7">
-        <v>2025</v>
-      </c>
-      <c r="N88" s="24">
-        <f>M88/100*20000*L88</f>
-        <v>567000</v>
-      </c>
-      <c r="P88" s="24" t="str">
-        <f t="shared" si="4"/>
-        <v>1,567000</v>
-      </c>
+      <c r="C88" s="27">
+        <v>18</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J88" s="19"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="22"/>
+      <c r="P88" s="22"/>
     </row>
     <row r="89" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="6">
-        <v>30007</v>
+        <v>30006</v>
       </c>
       <c r="B89" s="6">
         <v>3</v>
       </c>
-      <c r="C89" s="9">
-        <v>22</v>
-      </c>
-      <c r="D89" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="E89" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="F89" s="7" t="str">
+      <c r="C89" s="8">
+        <v>20</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F89" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>22级等级礼包</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H89" s="17"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="21"/>
-      <c r="K89" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L89" s="24">
-        <v>1.5</v>
-      </c>
-      <c r="M89" s="7">
-        <v>2700</v>
-      </c>
-      <c r="N89" s="24">
-        <f t="shared" ref="N89:N105" si="5">M89/100*20000*L89</f>
-        <v>810000</v>
-      </c>
-      <c r="P89" s="24" t="str">
+        <v>20级等级礼包</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H89" s="15"/>
+      <c r="I89" s="19"/>
+      <c r="J89" s="19"/>
+      <c r="K89" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L89" s="22">
+        <v>1.4</v>
+      </c>
+      <c r="M89" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N89" s="22">
+        <f>M89/100*20000*L89</f>
+        <v>567000</v>
+      </c>
+      <c r="P89" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,810000</v>
+        <v>1,567000</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="6">
-        <v>30008</v>
+        <v>30007</v>
       </c>
       <c r="B90" s="6">
         <v>3</v>
       </c>
-      <c r="C90" s="9">
-        <v>24</v>
-      </c>
-      <c r="D90" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="E90" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="F90" s="7" t="str">
+      <c r="C90" s="8">
+        <v>22</v>
+      </c>
+      <c r="D90" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F90" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>24级等级礼包</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="H90" s="17"/>
-      <c r="I90" s="7"/>
-      <c r="K90" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L90" s="24">
-        <v>1.6</v>
-      </c>
-      <c r="M90" s="7">
-        <v>3600</v>
-      </c>
-      <c r="N90" s="24">
-        <f t="shared" si="5"/>
-        <v>1152000</v>
-      </c>
-      <c r="P90" s="24" t="str">
+        <v>22级等级礼包</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H90" s="15"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="19"/>
+      <c r="K90" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L90" s="22">
+        <v>1.5</v>
+      </c>
+      <c r="M90" s="6">
+        <v>2700</v>
+      </c>
+      <c r="N90" s="22">
+        <f t="shared" ref="N90:N106" si="5">M90/100*20000*L90</f>
+        <v>810000</v>
+      </c>
+      <c r="P90" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1152000</v>
+        <v>1,810000</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="6">
-        <v>30009</v>
+        <v>30008</v>
       </c>
       <c r="B91" s="6">
         <v>3</v>
       </c>
-      <c r="C91" s="9">
-        <v>30</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="E91" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="F91" s="7" t="str">
+      <c r="C91" s="8">
+        <v>24</v>
+      </c>
+      <c r="D91" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F91" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>30级等级礼包</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H91" s="18"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="21"/>
-      <c r="K91" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L91" s="24">
-        <v>1.7</v>
-      </c>
-      <c r="M91" s="7">
-        <v>1450</v>
-      </c>
-      <c r="N91" s="24">
+        <v>24级等级礼包</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H91" s="15"/>
+      <c r="I91" s="6"/>
+      <c r="K91" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L91" s="22">
+        <v>1.6</v>
+      </c>
+      <c r="M91" s="6">
+        <v>3600</v>
+      </c>
+      <c r="N91" s="22">
         <f t="shared" si="5"/>
-        <v>493000</v>
-      </c>
-      <c r="P91" s="24" t="str">
+        <v>1152000</v>
+      </c>
+      <c r="P91" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,493000</v>
+        <v>1,1152000</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="6">
-        <v>30010</v>
+        <v>30009</v>
       </c>
       <c r="B92" s="6">
         <v>3</v>
       </c>
-      <c r="C92" s="9">
-        <v>31</v>
-      </c>
-      <c r="D92" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="E92" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="F92" s="7" t="str">
+      <c r="C92" s="8">
+        <v>30</v>
+      </c>
+      <c r="D92" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F92" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>31级等级礼包</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J92" s="21"/>
-      <c r="K92" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L92" s="24">
-        <v>1.8</v>
-      </c>
-      <c r="M92" s="7">
-        <v>2025</v>
-      </c>
-      <c r="N92" s="24">
+        <v>30级等级礼包</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H92" s="16"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="19"/>
+      <c r="K92" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L92" s="22">
+        <v>1.7</v>
+      </c>
+      <c r="M92" s="6">
+        <v>1450</v>
+      </c>
+      <c r="N92" s="22">
         <f t="shared" si="5"/>
-        <v>729000</v>
-      </c>
-      <c r="P92" s="24" t="str">
+        <v>493000</v>
+      </c>
+      <c r="P92" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,729000</v>
+        <v>1,493000</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="6">
-        <v>30011</v>
+        <v>30010</v>
       </c>
       <c r="B93" s="6">
         <v>3</v>
       </c>
-      <c r="C93" s="10">
-        <v>32</v>
-      </c>
-      <c r="D93" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="E93" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="F93" s="7" t="str">
+      <c r="C93" s="8">
+        <v>31</v>
+      </c>
+      <c r="D93" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F93" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>32级等级礼包</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="J93" s="21"/>
-      <c r="K93" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L93" s="24">
-        <v>1.9</v>
-      </c>
-      <c r="M93" s="7">
-        <v>2700</v>
-      </c>
-      <c r="N93" s="24">
+        <v>31级等级礼包</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J93" s="19"/>
+      <c r="K93" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L93" s="22">
+        <v>1.8</v>
+      </c>
+      <c r="M93" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N93" s="22">
         <f t="shared" si="5"/>
-        <v>1026000</v>
-      </c>
-      <c r="P93" s="24" t="str">
+        <v>729000</v>
+      </c>
+      <c r="P93" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1026000</v>
+        <v>1,729000</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="6">
-        <v>30012</v>
+        <v>30011</v>
       </c>
       <c r="B94" s="6">
         <v>3</v>
       </c>
-      <c r="C94" s="7">
-        <v>33</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="F94" s="7" t="str">
+      <c r="C94" s="9">
+        <v>32</v>
+      </c>
+      <c r="D94" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F94" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>33级等级礼包</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="J94" s="21"/>
-      <c r="K94" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L94" s="24">
-        <v>2</v>
-      </c>
-      <c r="M94" s="7">
-        <v>3600</v>
-      </c>
-      <c r="N94" s="24">
+        <v>32级等级礼包</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J94" s="19"/>
+      <c r="K94" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L94" s="22">
+        <v>1.9</v>
+      </c>
+      <c r="M94" s="6">
+        <v>2700</v>
+      </c>
+      <c r="N94" s="22">
         <f t="shared" si="5"/>
-        <v>1440000</v>
-      </c>
-      <c r="P94" s="24" t="str">
+        <v>1026000</v>
+      </c>
+      <c r="P94" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1440000</v>
+        <v>1,1026000</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="6">
-        <v>30013</v>
+        <v>30012</v>
       </c>
       <c r="B95" s="6">
         <v>3</v>
       </c>
-      <c r="C95" s="7">
-        <v>35</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="F95" s="7" t="str">
+      <c r="C95" s="6">
+        <v>33</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E95" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F95" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>35级等级礼包</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="J95" s="21"/>
-      <c r="K95" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="L95" s="24">
-        <v>2.1</v>
-      </c>
-      <c r="M95" s="7">
-        <v>4050</v>
-      </c>
-      <c r="N95" s="24">
+        <v>33级等级礼包</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J95" s="19"/>
+      <c r="K95" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L95" s="22">
+        <v>2</v>
+      </c>
+      <c r="M95" s="6">
+        <v>3600</v>
+      </c>
+      <c r="N95" s="22">
         <f t="shared" si="5"/>
-        <v>1701000</v>
-      </c>
-      <c r="P95" s="24" t="str">
+        <v>1440000</v>
+      </c>
+      <c r="P95" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1701000</v>
+        <v>1,1440000</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="6">
-        <v>30014</v>
+        <v>30013</v>
       </c>
       <c r="B96" s="6">
         <v>3</v>
       </c>
-      <c r="C96" s="7">
-        <v>40</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E96" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="F96" s="7" t="str">
+      <c r="C96" s="6">
+        <v>35</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F96" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>40级等级礼包</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="J96" s="21"/>
-      <c r="K96" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L96" s="24">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M96" s="7">
-        <v>1450</v>
-      </c>
-      <c r="N96" s="24">
+        <v>35级等级礼包</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J96" s="19"/>
+      <c r="K96" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L96" s="22">
+        <v>2.1</v>
+      </c>
+      <c r="M96" s="6">
+        <v>4050</v>
+      </c>
+      <c r="N96" s="22">
         <f t="shared" si="5"/>
-        <v>638000</v>
-      </c>
-      <c r="P96" s="24" t="str">
+        <v>1701000</v>
+      </c>
+      <c r="P96" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,638000</v>
+        <v>1,1701000</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="6">
-        <v>30015</v>
+        <v>30014</v>
       </c>
       <c r="B97" s="6">
         <v>3</v>
       </c>
-      <c r="C97" s="7">
-        <v>41</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E97" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F97" s="7" t="str">
+      <c r="C97" s="6">
+        <v>40</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F97" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>41级等级礼包</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L97" s="24">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M97" s="7">
-        <v>2025</v>
-      </c>
-      <c r="N97" s="24">
+        <v>40级等级礼包</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J97" s="19"/>
+      <c r="K97" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L97" s="22">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M97" s="6">
+        <v>1450</v>
+      </c>
+      <c r="N97" s="22">
         <f t="shared" si="5"/>
-        <v>931499.99999999988</v>
-      </c>
-      <c r="P97" s="24" t="str">
+        <v>638000</v>
+      </c>
+      <c r="P97" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,931500</v>
+        <v>1,638000</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="6">
-        <v>30016</v>
+        <v>30015</v>
       </c>
       <c r="B98" s="6">
         <v>3</v>
       </c>
-      <c r="C98" s="7">
-        <v>42</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E98" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F98" s="7" t="str">
+      <c r="C98" s="6">
+        <v>41</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F98" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>42级等级礼包</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="J98" s="21"/>
-      <c r="K98" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L98" s="24">
-        <v>2.4</v>
-      </c>
-      <c r="M98" s="7">
-        <v>2700</v>
-      </c>
-      <c r="N98" s="24">
+        <v>41级等级礼包</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L98" s="22">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M98" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N98" s="22">
         <f t="shared" si="5"/>
-        <v>1296000</v>
-      </c>
-      <c r="P98" s="24" t="str">
+        <v>931499.99999999988</v>
+      </c>
+      <c r="P98" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1296000</v>
+        <v>1,931500</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="6">
-        <v>30017</v>
+        <v>30016</v>
       </c>
       <c r="B99" s="6">
         <v>3</v>
       </c>
-      <c r="C99" s="7">
-        <v>43</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E99" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F99" s="7" t="str">
+      <c r="C99" s="6">
+        <v>42</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F99" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>43级等级礼包</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="J99" s="21"/>
-      <c r="K99" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L99" s="24">
-        <v>2.5</v>
-      </c>
-      <c r="M99" s="7">
-        <v>3600</v>
-      </c>
-      <c r="N99" s="24">
+        <v>42级等级礼包</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J99" s="19"/>
+      <c r="K99" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L99" s="22">
+        <v>2.4</v>
+      </c>
+      <c r="M99" s="6">
+        <v>2700</v>
+      </c>
+      <c r="N99" s="22">
         <f t="shared" si="5"/>
-        <v>1800000</v>
-      </c>
-      <c r="P99" s="24" t="str">
+        <v>1296000</v>
+      </c>
+      <c r="P99" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1800000</v>
+        <v>1,1296000</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="6">
-        <v>30018</v>
+        <v>30017</v>
       </c>
       <c r="B100" s="6">
         <v>3</v>
       </c>
-      <c r="C100" s="7">
-        <v>45</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E100" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F100" s="7" t="str">
+      <c r="C100" s="6">
+        <v>43</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F100" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>45级等级礼包</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="J100" s="21"/>
-      <c r="K100" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="L100" s="24">
-        <v>2.6</v>
-      </c>
-      <c r="M100" s="7">
-        <v>4050</v>
-      </c>
-      <c r="N100" s="24">
+        <v>43级等级礼包</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="J100" s="19"/>
+      <c r="K100" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L100" s="22">
+        <v>2.5</v>
+      </c>
+      <c r="M100" s="6">
+        <v>3600</v>
+      </c>
+      <c r="N100" s="22">
         <f t="shared" si="5"/>
-        <v>2106000</v>
-      </c>
-      <c r="P100" s="24" t="str">
+        <v>1800000</v>
+      </c>
+      <c r="P100" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,2106000</v>
+        <v>1,1800000</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="6">
-        <v>30019</v>
+        <v>30018</v>
       </c>
       <c r="B101" s="6">
         <v>3</v>
       </c>
-      <c r="C101" s="7">
-        <v>50</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E101" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F101" s="7" t="str">
+      <c r="C101" s="6">
+        <v>45</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F101" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>50级等级礼包</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="K101" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L101" s="24">
-        <v>2.7</v>
-      </c>
-      <c r="M101" s="7">
-        <v>1450</v>
-      </c>
-      <c r="N101" s="24">
+        <v>45级等级礼包</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J101" s="19"/>
+      <c r="K101" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L101" s="22">
+        <v>2.6</v>
+      </c>
+      <c r="M101" s="6">
+        <v>4050</v>
+      </c>
+      <c r="N101" s="22">
         <f t="shared" si="5"/>
-        <v>783000</v>
-      </c>
-      <c r="P101" s="24" t="str">
+        <v>2106000</v>
+      </c>
+      <c r="P101" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,783000</v>
+        <v>1,2106000</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="6">
-        <v>30020</v>
+        <v>30019</v>
       </c>
       <c r="B102" s="6">
         <v>3</v>
       </c>
-      <c r="C102" s="7">
-        <v>51</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E102" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="F102" s="7" t="str">
+      <c r="C102" s="6">
+        <v>50</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="F102" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>51级等级礼包</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="J102" s="21"/>
-      <c r="K102" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L102" s="24">
-        <v>2.8</v>
-      </c>
-      <c r="M102" s="7">
-        <v>2025</v>
-      </c>
-      <c r="N102" s="24">
+        <v>50级等级礼包</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L102" s="22">
+        <v>2.7</v>
+      </c>
+      <c r="M102" s="6">
+        <v>1450</v>
+      </c>
+      <c r="N102" s="22">
         <f t="shared" si="5"/>
-        <v>1134000</v>
-      </c>
-      <c r="P102" s="24" t="str">
+        <v>783000</v>
+      </c>
+      <c r="P102" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1134000</v>
+        <v>1,783000</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="6">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B103" s="6">
         <v>3</v>
       </c>
-      <c r="C103" s="7">
-        <v>52</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E103" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="F103" s="7" t="str">
+      <c r="C103" s="6">
+        <v>51</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F103" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>52级等级礼包</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="J103" s="21"/>
-      <c r="K103" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L103" s="24">
-        <v>2.9</v>
-      </c>
-      <c r="M103" s="7">
-        <v>2700</v>
-      </c>
-      <c r="N103" s="24">
+        <v>51级等级礼包</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="J103" s="19"/>
+      <c r="K103" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L103" s="22">
+        <v>2.8</v>
+      </c>
+      <c r="M103" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N103" s="22">
         <f t="shared" si="5"/>
-        <v>1566000</v>
-      </c>
-      <c r="P103" s="24" t="str">
+        <v>1134000</v>
+      </c>
+      <c r="P103" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,1566000</v>
+        <v>1,1134000</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="6">
-        <v>30022</v>
+        <v>30021</v>
       </c>
       <c r="B104" s="6">
         <v>3</v>
       </c>
-      <c r="C104" s="7">
-        <v>53</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E104" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F104" s="7" t="str">
+      <c r="C104" s="6">
+        <v>52</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F104" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>53级等级礼包</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="J104" s="21"/>
-      <c r="K104" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L104" s="24">
-        <v>3</v>
-      </c>
-      <c r="M104" s="7">
-        <v>3600</v>
-      </c>
-      <c r="N104" s="24">
+        <v>52级等级礼包</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J104" s="19"/>
+      <c r="K104" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L104" s="22">
+        <v>2.9</v>
+      </c>
+      <c r="M104" s="6">
+        <v>2700</v>
+      </c>
+      <c r="N104" s="22">
         <f t="shared" si="5"/>
-        <v>2160000</v>
-      </c>
-      <c r="P104" s="24" t="str">
+        <v>1566000</v>
+      </c>
+      <c r="P104" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,2160000</v>
+        <v>1,1566000</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="6">
-        <v>30023</v>
+        <v>30022</v>
       </c>
       <c r="B105" s="6">
         <v>3</v>
       </c>
-      <c r="C105" s="7">
-        <v>55</v>
-      </c>
-      <c r="D105" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E105" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="F105" s="7" t="str">
+      <c r="C105" s="6">
+        <v>53</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F105" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
-        <v>55级等级礼包</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="J105" s="21"/>
-      <c r="K105" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="L105" s="24">
+        <v>53级等级礼包</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J105" s="19"/>
+      <c r="K105" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L105" s="22">
         <v>3</v>
       </c>
-      <c r="M105" s="25">
-        <v>4050</v>
-      </c>
-      <c r="N105" s="24">
+      <c r="M105" s="6">
+        <v>3600</v>
+      </c>
+      <c r="N105" s="22">
         <f t="shared" si="5"/>
-        <v>2430000</v>
-      </c>
-      <c r="P105" s="24" t="str">
+        <v>2160000</v>
+      </c>
+      <c r="P105" s="22" t="str">
         <f t="shared" si="4"/>
-        <v>1,2430000</v>
+        <v>1,2160000</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="6">
-        <v>40001</v>
+        <v>30023</v>
       </c>
       <c r="B106" s="6">
-        <v>4</v>
-      </c>
-      <c r="C106" s="7">
-        <v>8</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E106" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="F106" s="7" t="str">
-        <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>8级免费礼包</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>197</v>
+        <v>3</v>
+      </c>
+      <c r="C106" s="6">
+        <v>55</v>
+      </c>
+      <c r="D106" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F106" s="6" t="str">
+        <f>表1[[#This Row],[Par_1]]&amp;"级等级礼包"</f>
+        <v>55级等级礼包</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J106" s="19"/>
+      <c r="K106" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L106" s="22">
+        <v>3</v>
+      </c>
+      <c r="M106" s="23">
+        <v>4050</v>
+      </c>
+      <c r="N106" s="22">
+        <f t="shared" si="5"/>
+        <v>2430000</v>
+      </c>
+      <c r="P106" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v>1,2430000</v>
       </c>
     </row>
     <row r="107" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="6">
-        <v>40002</v>
+        <v>40001</v>
       </c>
       <c r="B107" s="6">
         <v>4</v>
       </c>
-      <c r="C107" s="7">
+      <c r="C107" s="6">
+        <v>8</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E107" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="F107" s="6" t="str">
+        <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
+        <v>8级免费礼包</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="6">
+        <v>40002</v>
+      </c>
+      <c r="B108" s="6">
+        <v>4</v>
+      </c>
+      <c r="C108" s="6">
         <v>12</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D108" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E107" s="26" t="s">
+      <c r="E108" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="F107" s="7" t="str">
+      <c r="F108" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>12级免费礼包</v>
       </c>
-      <c r="G107" s="7" t="s">
+      <c r="G108" s="6" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="108" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="6">
+    <row r="109" spans="1:16" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="6">
         <v>40003</v>
       </c>
-      <c r="B108" s="6">
+      <c r="B109" s="6">
         <v>4</v>
       </c>
-      <c r="C108" s="7">
+      <c r="C109" s="6">
         <v>16</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D109" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E108" s="26" t="s">
+      <c r="E109" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="F108" s="7" t="str">
+      <c r="F109" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>16级免费礼包</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G109" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="109" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="6">
+    <row r="110" spans="1:16" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="6">
         <v>40004</v>
       </c>
-      <c r="B109" s="6">
+      <c r="B110" s="6">
         <v>4</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C110" s="6">
         <v>18</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D110" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E109" s="26" t="s">
+      <c r="E110" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="F109" s="7" t="str">
+      <c r="F110" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>18级免费礼包</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="G110" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="110" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="6">
+    <row r="111" spans="1:16" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="6">
         <v>40005</v>
       </c>
-      <c r="B110" s="6">
+      <c r="B111" s="6">
         <v>4</v>
       </c>
-      <c r="C110" s="7">
+      <c r="C111" s="6">
         <v>21</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D111" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E110" s="26" t="s">
+      <c r="E111" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="F110" s="7" t="str">
+      <c r="F111" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>21级免费礼包</v>
       </c>
-      <c r="G110" s="7" t="s">
+      <c r="G111" s="6" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="6">
+    <row r="112" spans="1:16" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="6">
         <v>40006</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B112" s="6">
         <v>4</v>
       </c>
-      <c r="C111" s="7">
+      <c r="C112" s="6">
         <v>23</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D112" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E111" s="26" t="s">
+      <c r="E112" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="F111" s="7" t="str">
+      <c r="F112" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>23级免费礼包</v>
       </c>
-      <c r="G111" s="7" t="s">
+      <c r="G112" s="6" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="112" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="6">
+    <row r="113" spans="1:7" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="6">
         <v>40007</v>
       </c>
-      <c r="B112" s="6">
+      <c r="B113" s="6">
         <v>4</v>
       </c>
-      <c r="C112" s="7">
+      <c r="C113" s="6">
         <v>25</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D113" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E112" s="26" t="s">
+      <c r="E113" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="F112" s="7" t="str">
+      <c r="F113" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>25级免费礼包</v>
       </c>
-      <c r="G112" s="7" t="s">
+      <c r="G113" s="6" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="113" spans="1:7" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="6">
+    <row r="114" spans="1:7" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="6">
         <v>40008</v>
       </c>
-      <c r="B113" s="6">
+      <c r="B114" s="6">
         <v>4</v>
       </c>
-      <c r="C113" s="7">
+      <c r="C114" s="6">
         <v>27</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D114" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E113" s="26" t="s">
+      <c r="E114" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="F113" s="7" t="str">
+      <c r="F114" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>27级免费礼包</v>
       </c>
-      <c r="G113" s="7" t="s">
+      <c r="G114" s="6" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="114" spans="1:7" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="6">
+    <row r="115" spans="1:7" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="6">
         <v>40009</v>
       </c>
-      <c r="B114" s="6">
+      <c r="B115" s="6">
         <v>4</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C115" s="6">
         <v>29</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D115" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E114" s="26" t="s">
+      <c r="E115" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="F114" s="7" t="str">
+      <c r="F115" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>29级免费礼包</v>
       </c>
-      <c r="G114" s="7" t="s">
+      <c r="G115" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="115" spans="1:7" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="6">
+    <row r="116" spans="1:7" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A116" s="6">
         <v>40010</v>
       </c>
-      <c r="B115" s="6">
+      <c r="B116" s="6">
         <v>4</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C116" s="6">
         <v>31</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D116" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E115" s="26" t="s">
+      <c r="E116" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="F115" s="7" t="str">
+      <c r="F116" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>31级免费礼包</v>
       </c>
-      <c r="G115" s="7" t="s">
+      <c r="G116" s="6" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="116" spans="1:7" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="6">
+    <row r="117" spans="1:7" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A117" s="6">
         <v>40011</v>
       </c>
-      <c r="B116" s="6">
+      <c r="B117" s="6">
         <v>4</v>
       </c>
-      <c r="C116" s="7">
+      <c r="C117" s="6">
         <v>33</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D117" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E116" s="26" t="s">
+      <c r="E117" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="F116" s="7" t="str">
+      <c r="F117" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>33级免费礼包</v>
       </c>
-      <c r="G116" s="7" t="s">
+      <c r="G117" s="6" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="117" spans="1:7" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="6">
+    <row r="118" spans="1:7" s="18" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A118" s="6">
         <v>40012</v>
       </c>
-      <c r="B117" s="6">
+      <c r="B118" s="6">
         <v>4</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C118" s="6">
         <v>35</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D118" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E117" s="26" t="s">
+      <c r="E118" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="F117" s="7" t="str">
+      <c r="F118" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>35级免费礼包</v>
       </c>
-      <c r="G117" s="7" t="s">
+      <c r="G118" s="6" t="s">
         <v>208</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A118" s="6">
-        <v>40013</v>
-      </c>
-      <c r="B118" s="6">
-        <v>4</v>
-      </c>
-      <c r="C118" s="7">
-        <v>37</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E118" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="F118" s="7" t="str">
-        <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>37级免费礼包</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="6">
-        <v>40014</v>
+        <v>40013</v>
       </c>
       <c r="B119" s="6">
         <v>4</v>
       </c>
-      <c r="C119" s="7">
-        <v>39</v>
-      </c>
-      <c r="D119" s="7" t="s">
+      <c r="C119" s="6">
+        <v>37</v>
+      </c>
+      <c r="D119" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E119" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="F119" s="7" t="str">
+      <c r="E119" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="F119" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>39级免费礼包</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>210</v>
+        <v>37级免费礼包</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="6">
-        <v>40015</v>
+        <v>40014</v>
       </c>
       <c r="B120" s="6">
         <v>4</v>
       </c>
-      <c r="C120" s="7">
-        <v>41</v>
-      </c>
-      <c r="D120" s="7" t="s">
+      <c r="C120" s="6">
+        <v>39</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E120" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="F120" s="7" t="str">
+      <c r="E120" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="F120" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>41级免费礼包</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>211</v>
+        <v>39级免费礼包</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="6">
-        <v>40016</v>
+        <v>40015</v>
       </c>
       <c r="B121" s="6">
         <v>4</v>
       </c>
-      <c r="C121" s="7">
-        <v>43</v>
-      </c>
-      <c r="D121" s="7" t="s">
+      <c r="C121" s="6">
+        <v>41</v>
+      </c>
+      <c r="D121" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E121" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="F121" s="7" t="str">
+      <c r="E121" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="F121" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>43级免费礼包</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>212</v>
+        <v>41级免费礼包</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="6">
-        <v>40017</v>
+        <v>40016</v>
       </c>
       <c r="B122" s="6">
         <v>4</v>
       </c>
-      <c r="C122" s="7">
-        <v>45</v>
-      </c>
-      <c r="D122" s="7" t="s">
+      <c r="C122" s="6">
+        <v>43</v>
+      </c>
+      <c r="D122" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E122" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="F122" s="7" t="str">
+      <c r="E122" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F122" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>45级免费礼包</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>213</v>
+        <v>43级免费礼包</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="6">
-        <v>40018</v>
+        <v>40017</v>
       </c>
       <c r="B123" s="6">
         <v>4</v>
       </c>
-      <c r="C123" s="7">
-        <v>47</v>
-      </c>
-      <c r="D123" s="7" t="s">
+      <c r="C123" s="6">
+        <v>45</v>
+      </c>
+      <c r="D123" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E123" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="F123" s="7" t="str">
+      <c r="E123" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F123" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>47级免费礼包</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>214</v>
+        <v>45级免费礼包</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="6">
-        <v>40019</v>
+        <v>40018</v>
       </c>
       <c r="B124" s="6">
         <v>4</v>
       </c>
-      <c r="C124" s="7">
-        <v>49</v>
-      </c>
-      <c r="D124" s="7" t="s">
+      <c r="C124" s="6">
+        <v>47</v>
+      </c>
+      <c r="D124" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E124" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="F124" s="7" t="str">
+      <c r="E124" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="F124" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
-        <v>49级免费礼包</v>
-      </c>
-      <c r="G124" s="7" t="s">
-        <v>215</v>
+        <v>47级免费礼包</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="6">
-        <v>40020</v>
+        <v>40019</v>
       </c>
       <c r="B125" s="6">
         <v>4</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="6">
+        <v>49</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E125" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F125" s="6" t="str">
+        <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
+        <v>49级免费礼包</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="6">
+        <v>40020</v>
+      </c>
+      <c r="B126" s="6">
+        <v>4</v>
+      </c>
+      <c r="C126" s="6">
         <v>50</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="D126" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E125" s="26" t="s">
+      <c r="E126" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="F125" s="7" t="str">
+      <c r="F126" s="6" t="str">
         <f>表1[[#This Row],[Par_1]]&amp;"级免费礼包"</f>
         <v>50级免费礼包</v>
       </c>
-      <c r="G125" s="7" t="s">
+      <c r="G126" s="6" t="s">
         <v>216</v>
       </c>
     </row>
